--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487664_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487664_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4685</v>
+        <v>5.0324</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3767</v>
+        <v>6.7771</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9082</v>
+        <v>-1.7447</v>
       </c>
       <c r="G2" t="n">
         <v>2.6153</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6065</v>
+        <v>-0.0426</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4229</v>
+        <v>-0.0225</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1837</v>
+        <v>-0.0202</v>
       </c>
       <c r="V2" t="n">
         <v>1.1015</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4346</v>
+        <v>2.2255</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6927</v>
+        <v>2.5926</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2581</v>
+        <v>-0.3671</v>
       </c>
       <c r="G3" t="n">
         <v>0.2101</v>
@@ -688,13 +688,13 @@
         <v>0.7761</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.4214</v>
       </c>
       <c r="T3" t="n">
-        <v>0.729</v>
+        <v>0.6289</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0984</v>
+        <v>-0.2075</v>
       </c>
       <c r="V3" t="n">
         <v>1.788</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2085</v>
+        <v>1.9543</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7144</v>
+        <v>2.8145</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5059</v>
+        <v>-0.8602</v>
       </c>
       <c r="G4" t="n">
         <v>2.5298</v>
@@ -766,13 +766,13 @@
         <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8786</v>
+        <v>0.6244</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3656</v>
+        <v>0.4657</v>
       </c>
       <c r="U4" t="n">
-        <v>0.513</v>
+        <v>0.1587</v>
       </c>
       <c r="V4" t="n">
         <v>-1.394</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5545</v>
+        <v>0.9371</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9093</v>
+        <v>-0.3087</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4638</v>
+        <v>1.2458</v>
       </c>
       <c r="G5" t="n">
         <v>0.7806999999999999</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2799</v>
+        <v>0.1026</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7863</v>
+        <v>-0.1857</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5063</v>
+        <v>0.2883</v>
       </c>
       <c r="V5" t="n">
         <v>0.4418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2973</v>
+        <v>0.4502</v>
       </c>
       <c r="E6" t="n">
+        <v>-0.1025</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5527</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0478</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.5522</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.5044</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.0704</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.0298</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5223</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.545</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.3881</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="F6" t="n">
-        <v>1.2675</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.5454</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.2554</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-0.8008</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-1.3347</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-1.3347</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7893</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.2554</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.5339</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6487000000000001</v>
+        <v>-0.2094</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3645</v>
+        <v>-0.2027</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2842</v>
+        <v>-0.0067</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2956</v>
+        <v>0.1585</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2026</v>
+        <v>0.3005</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4982</v>
+        <v>-0.142</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0478</v>
+        <v>-0.4614</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5522</v>
+        <v>-1.3956</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5044</v>
+        <v>0.9343</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0704</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0298</v>
+        <v>-1.277</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0406</v>
+        <v>1.3625</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0227</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5223</v>
+        <v>-0.1187</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.545</v>
+        <v>-0.4282</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3641</v>
+        <v>-0.0906</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>0.3866</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0612</v>
+        <v>-0.4772</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5164</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.7985</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. DE LA CRUZ DE LA ROSA</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2469</v>
+        <v>0.0154</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1685</v>
+        <v>-1.1704</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4153</v>
+        <v>1.1857</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.236</v>
+        <v>-0.5454</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0132</v>
+        <v>0.2554</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2492</v>
+        <v>-0.8008</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0883</v>
+        <v>-1.3347</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5049</v>
+        <v>-1.3347</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3242</v>
+        <v>0.7893</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.58</v>
+        <v>0.2554</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2558</v>
+        <v>0.5339</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.194</v>
+        <v>0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1395</v>
+        <v>0.3668</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1806</v>
+        <v>0.1643</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3201</v>
+        <v>0.2025</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5373</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>L. DE LA CRUZ DE LA ROSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0351</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4006</v>
+        <v>-0.3687</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4963</v>
+        <v>0.3336</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4614</v>
+        <v>-0.236</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3956</v>
+        <v>0.0132</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9343</v>
+        <v>-0.2492</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0883</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.277</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3625</v>
+        <v>-0.5049</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.3242</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1187</v>
+        <v>-0.58</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4282</v>
+        <v>0.2558</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>-0.194</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3448</v>
+        <v>-0.1424</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4867</v>
+        <v>-0.3808</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8315</v>
+        <v>0.2384</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5164</v>
+        <v>0.5373</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7985</v>
+        <v>0.894</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>-0.3567</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7965</v>
+        <v>-1.0151</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4547</v>
+        <v>-1.755</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6582</v>
+        <v>0.7399</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0115</v>
@@ -1234,13 +1234,13 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2732</v>
+        <v>0.0547</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1828</v>
+        <v>-0.1175</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.1722</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2821</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5518</v>
+        <v>-2.6796</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6764</v>
+        <v>-2.4772</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1246</v>
+        <v>-0.2024</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7113</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8311</v>
+        <v>0.7032</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0329</v>
+        <v>0.2321</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7982</v>
+        <v>0.4711</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8358</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3218</v>
+        <v>-3.3034</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7726</v>
+        <v>-3.2721</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5491</v>
+        <v>-0.0313</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5509</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2306</v>
+        <v>-0.2123</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9085</v>
+        <v>-0.408</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3221</v>
+        <v>0.1957</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3463</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7401</v>
+        <v>3.7402</v>
       </c>
       <c r="E13" t="n">
         <v>3.030099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7100000000000005</v>
+        <v>0.7100000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>1.667199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.033799999999999</v>
+        <v>-5.0338</v>
       </c>
       <c r="I13" t="n">
         <v>6.701100000000001</v>
@@ -1468,10 +1468,10 @@
         <v>9.701499999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5757</v>
+        <v>1.5758</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5603999999999999</v>
+        <v>0.5604000000000002</v>
       </c>
       <c r="U13" t="n">
         <v>1.0153</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.903</v>
+        <v>6.958</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6343</v>
+        <v>5.335</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2688</v>
+        <v>1.6231</v>
       </c>
       <c r="G14" t="n">
         <v>4.1796</v>
@@ -1546,13 +1546,13 @@
         <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2615</v>
+        <v>-1.2065</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.6353</v>
+        <v>-0.9346</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6263</v>
+        <v>-0.2719</v>
       </c>
       <c r="V14" t="n">
         <v>6.1194</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.454</v>
+        <v>5.0546</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1106</v>
+        <v>3.7112</v>
       </c>
       <c r="F15" t="n">
         <v>1.3434</v>
@@ -1624,10 +1624,10 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7526</v>
+        <v>-0.152</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6651</v>
+        <v>-0.0645</v>
       </c>
       <c r="U15" t="n">
         <v>-0.08740000000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1264</v>
+        <v>0.2988</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8532</v>
+        <v>1.7531</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7269</v>
+        <v>-1.4543</v>
       </c>
       <c r="G16" t="n">
         <v>0.4197</v>
@@ -1702,13 +1702,13 @@
         <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0112</v>
+        <v>0.1612</v>
       </c>
       <c r="T16" t="n">
-        <v>0.305</v>
+        <v>0.2049</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3163</v>
+        <v>-0.0437</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2821</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4774</v>
+        <v>-0.8778</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7496</v>
+        <v>-2.15</v>
       </c>
       <c r="F17" t="n">
         <v>1.2722</v>
@@ -1780,10 +1780,10 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>0.231</v>
+        <v>-0.1694</v>
       </c>
       <c r="T17" t="n">
-        <v>0.185</v>
+        <v>-0.2154</v>
       </c>
       <c r="U17" t="n">
         <v>0.046</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7827</v>
+        <v>-0.914</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5771</v>
+        <v>-1.2713</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3598</v>
+        <v>0.3574</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8526</v>
+        <v>-0.7098</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0177</v>
+        <v>0.5026</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1651</v>
+        <v>-1.2123</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8054</v>
+        <v>-0.6261</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6025</v>
+        <v>0.0412</v>
       </c>
       <c r="L18" t="n">
-        <v>0.203</v>
+        <v>-0.6673</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9529</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4152</v>
+        <v>0.4614</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3681</v>
+        <v>-0.545</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1063</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1806</v>
+        <v>0.325</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2647</v>
+        <v>-0.2187</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4955</v>
+        <v>0.6597</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4477</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-1.1553</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1712</v>
+        <v>1.477</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2483</v>
+        <v>-2.6323</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7098</v>
+        <v>0.8526</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5026</v>
+        <v>2.0177</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2123</v>
+        <v>-1.1651</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6261</v>
+        <v>1.8054</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0412</v>
+        <v>1.6025</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6673</v>
+        <v>0.203</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.9529</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4614</v>
+        <v>0.4152</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.545</v>
+        <v>-1.3681</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0973</v>
+        <v>-0.2885</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4251</v>
+        <v>-0.2807</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3277</v>
+        <v>-0.0078</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6597</v>
+        <v>-2.4955</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6597</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.012</v>
+        <v>-1.2757</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5963</v>
+        <v>-1.6964</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5843</v>
+        <v>0.4207</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1779</v>
@@ -2014,13 +2014,13 @@
         <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5942</v>
+        <v>0.3306</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3645</v>
+        <v>0.2644</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2297</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0.3776</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. PEÑA LOPEZ</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3693</v>
+        <v>-3.3345</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8023</v>
+        <v>-0.9144</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-2.4202</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0431</v>
+        <v>-1.9215</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.492</v>
+        <v>2.2088</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5511</v>
+        <v>-4.1303</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.4528</v>
+        <v>-0.8698</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2399</v>
+        <v>1.0916</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2129</v>
+        <v>-1.9614</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4096</v>
+        <v>-1.0517</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2521</v>
+        <v>1.1172</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6618000000000001</v>
+        <v>-2.1689</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4605</v>
+        <v>0.0451</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3017</v>
+        <v>-0.0446</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1588</v>
+        <v>0.0897</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8358</v>
+        <v>-1.4582</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.788</v>
+        <v>-1.4582</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>O. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5625</v>
+        <v>-3.4149</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4149</v>
+        <v>-2.9024</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1476</v>
+        <v>-0.5125</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9215</v>
+        <v>-2.0431</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2088</v>
+        <v>-1.492</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.1303</v>
+        <v>-0.5511</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8698</v>
+        <v>-2.4528</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0916</v>
+        <v>-1.2399</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9614</v>
+        <v>-1.2129</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0517</v>
+        <v>0.4096</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1172</v>
+        <v>-0.2521</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1689</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1828</v>
+        <v>-0.5061</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5451</v>
+        <v>-0.4018</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3623</v>
+        <v>-0.1043</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4582</v>
+        <v>-1.8358</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4582</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0968</v>
+        <v>-5.0794</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1509</v>
+        <v>-4.0518</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9459</v>
+        <v>-1.0276</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4531</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0861</v>
+        <v>0.1035</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0329</v>
+        <v>0.132</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0532</v>
+        <v>-0.0286</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7298</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7402</v>
+        <v>-3.740200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7100000000000009</v>
+        <v>-0.7100000000000017</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0302</v>
+        <v>-3.0301</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6673</v>
@@ -2296,16 +2296,16 @@
         <v>5.034000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.7011</v>
+        <v>-6.701100000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>1.018900000000002</v>
+        <v>1.018900000000001</v>
       </c>
       <c r="K24" t="n">
         <v>1.491299999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4724000000000002</v>
+        <v>-0.4723999999999997</v>
       </c>
       <c r="M24" t="n">
         <v>-2.6864</v>
@@ -2323,22 +2323,22 @@
         <v>-9.701700000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>8.731499999999999</v>
+        <v>8.7315</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.575899999999999</v>
+        <v>-1.5758</v>
       </c>
       <c r="T24" t="n">
         <v>-1.0153</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5605999999999999</v>
+        <v>-0.5605</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4731999999999994</v>
+        <v>0.4732000000000003</v>
       </c>
       <c r="W24" t="n">
-        <v>8.987900000000002</v>
+        <v>8.9879</v>
       </c>
       <c r="X24" t="n">
         <v>-8.514700000000001</v>
